--- a/khuvuc.xlsx
+++ b/khuvuc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B6C67E-6128-473C-A8A5-629DAA463BEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C75F125-7077-481A-BD6E-9157CC06B369}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-84" windowWidth="23256" windowHeight="12456" xr2:uid="{3188401B-A849-455B-B56A-849927DD752C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3188401B-A849-455B-B56A-849927DD752C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4200,7 +4200,7 @@
         <v>76</v>
       </c>
       <c r="G70" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="4">
         <v>24</v>
@@ -4487,7 +4487,7 @@
         <v>132</v>
       </c>
       <c r="K77" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="4">
         <v>2</v>
@@ -5138,7 +5138,7 @@
         <v>158</v>
       </c>
       <c r="G94" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="4">
         <v>7</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="J96" s="4"/>
       <c r="K96" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="4">
         <v>6</v>
@@ -9695,7 +9695,7 @@
         <v>0</v>
       </c>
       <c r="G223" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H223" s="4">
         <v>419</v>
@@ -9761,7 +9761,7 @@
         <v>0</v>
       </c>
       <c r="G225" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H225" s="4">
         <v>227</v>
@@ -10531,7 +10531,7 @@
         <v>70</v>
       </c>
       <c r="G247" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H247" s="4">
         <v>43</v>
@@ -10679,7 +10679,7 @@
         <v>88</v>
       </c>
       <c r="G251" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H251" s="4">
         <v>55</v>
@@ -12620,7 +12620,7 @@
         <v>207</v>
       </c>
       <c r="G304" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H304" s="4">
         <v>141</v>

--- a/khuvuc.xlsx
+++ b/khuvuc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VisualCodeWorkspace\PythonWeb\thongkenhaplieu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF5434F-078E-490D-ADE8-47A2A8077479}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47E49B8-8C91-4FF4-865D-3F3958B49558}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3188401B-A849-455B-B56A-849927DD752C}"/>
   </bookViews>
